--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1252,6 +1252,2008 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120168800</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>498529</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7085325</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120168794</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>498683</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7085502</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120168797</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>498629</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7085387</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120168806</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>498639</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7085616</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120168803</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91005</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>498551</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7085554</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120168792</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>498703</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7085620</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120168787</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>498559</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7085553</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120168788</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>498509</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7085469</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120168795</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>498621</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7085423</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120168808</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>498735</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7085566</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120168802</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>498710</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7085620</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120168804</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90558</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>498644</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7085616</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120168810</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>498501</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7085330</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt i omgivningen</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120168798</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>498592</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7085385</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120168793</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>498764</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7085585</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120168791</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>498655</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7085609</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120168807</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>498649</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7085609</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120168809</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>498628</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7085357</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120168789</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mannabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>498570</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7085548</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1255,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168800</v>
+        <v>120168788</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498529</v>
+        <v>498509</v>
       </c>
       <c r="R7" t="n">
-        <v>7085325</v>
+        <v>7085469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168794</v>
+        <v>120168789</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498683</v>
+        <v>498570</v>
       </c>
       <c r="R8" t="n">
-        <v>7085502</v>
+        <v>7085548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168797</v>
+        <v>120168798</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498629</v>
+        <v>498592</v>
       </c>
       <c r="R9" t="n">
-        <v>7085387</v>
+        <v>7085385</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168803</v>
+        <v>120168794</v>
       </c>
       <c r="B11" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,25 +1690,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498551</v>
+        <v>498683</v>
       </c>
       <c r="R11" t="n">
-        <v>7085554</v>
+        <v>7085502</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1754,6 +1754,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168792</v>
+        <v>120168810</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,34 +1801,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498703</v>
+        <v>498501</v>
       </c>
       <c r="R12" t="n">
-        <v>7085620</v>
+        <v>7085330</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1868,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt i omgivningen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,6 +1877,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1887,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168787</v>
+        <v>120168800</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498559</v>
+        <v>498529</v>
       </c>
       <c r="R13" t="n">
-        <v>7085553</v>
+        <v>7085325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,6 +1972,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168788</v>
+        <v>120168802</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,16 +2019,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2029,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498509</v>
+        <v>498710</v>
       </c>
       <c r="R14" t="n">
-        <v>7085469</v>
+        <v>7085620</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,7 +2083,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,10 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168795</v>
+        <v>120168787</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,21 +2126,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2136,10 +2150,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498621</v>
+        <v>498559</v>
       </c>
       <c r="R15" t="n">
-        <v>7085423</v>
+        <v>7085553</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,11 +2186,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,10 +2212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168808</v>
+        <v>120168792</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2219,21 +2228,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2243,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498735</v>
+        <v>498703</v>
       </c>
       <c r="R16" t="n">
-        <v>7085566</v>
+        <v>7085620</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2279,6 +2288,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168802</v>
+        <v>120168795</v>
       </c>
       <c r="B17" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,16 +2335,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2345,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498710</v>
+        <v>498621</v>
       </c>
       <c r="R17" t="n">
-        <v>7085620</v>
+        <v>7085423</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,7 +2399,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168810</v>
+        <v>120168803</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>91005</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2526,41 +2540,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498501</v>
+        <v>498551</v>
       </c>
       <c r="R19" t="n">
-        <v>7085330</v>
+        <v>7085554</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,18 +2606,12 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt i omgivningen</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2625,7 +2630,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168798</v>
+        <v>120168793</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2665,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498592</v>
+        <v>498764</v>
       </c>
       <c r="R20" t="n">
-        <v>7085385</v>
+        <v>7085585</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2710,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168793</v>
+        <v>120168809</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,21 +2753,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2772,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498764</v>
+        <v>498628</v>
       </c>
       <c r="R21" t="n">
-        <v>7085585</v>
+        <v>7085357</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,11 +2813,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168791</v>
+        <v>120168808</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,21 +2855,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498655</v>
+        <v>498735</v>
       </c>
       <c r="R22" t="n">
-        <v>7085609</v>
+        <v>7085566</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,11 +2915,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2946,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168807</v>
+        <v>120168797</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,21 +2957,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2986,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498649</v>
+        <v>498629</v>
       </c>
       <c r="R23" t="n">
-        <v>7085609</v>
+        <v>7085387</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,6 +3017,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3048,10 +3048,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120168809</v>
+        <v>120168791</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498628</v>
+        <v>498655</v>
       </c>
       <c r="R24" t="n">
-        <v>7085357</v>
+        <v>7085609</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,6 +3124,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120168789</v>
+        <v>120168807</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,21 +3171,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3190,10 +3195,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498570</v>
+        <v>498649</v>
       </c>
       <c r="R25" t="n">
-        <v>7085548</v>
+        <v>7085609</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,11 +3231,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168788</v>
+        <v>120168807</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498509</v>
+        <v>498649</v>
       </c>
       <c r="R7" t="n">
-        <v>7085469</v>
+        <v>7085609</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,11 +1331,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168789</v>
+        <v>120168809</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498570</v>
+        <v>498628</v>
       </c>
       <c r="R8" t="n">
-        <v>7085548</v>
+        <v>7085357</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,11 +1433,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168798</v>
+        <v>120168808</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498592</v>
+        <v>498735</v>
       </c>
       <c r="R9" t="n">
-        <v>7085385</v>
+        <v>7085566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,11 +1535,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1678,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168794</v>
+        <v>120168795</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1718,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498683</v>
+        <v>498621</v>
       </c>
       <c r="R11" t="n">
-        <v>7085502</v>
+        <v>7085423</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168810</v>
+        <v>120168798</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,37 +1786,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498501</v>
+        <v>498592</v>
       </c>
       <c r="R12" t="n">
-        <v>7085330</v>
+        <v>7085385</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt i omgivningen</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,7 +1859,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1896,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168800</v>
+        <v>120168810</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,34 +1893,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498529</v>
+        <v>498501</v>
       </c>
       <c r="R13" t="n">
-        <v>7085325</v>
+        <v>7085330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,7 +1960,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt i omgivningen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,6 +1969,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2003,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168802</v>
+        <v>120168794</v>
       </c>
       <c r="B14" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,16 +2004,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2043,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498710</v>
+        <v>498683</v>
       </c>
       <c r="R14" t="n">
-        <v>7085620</v>
+        <v>7085502</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,7 +2068,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168787</v>
+        <v>120168791</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2150,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498559</v>
+        <v>498655</v>
       </c>
       <c r="R15" t="n">
-        <v>7085553</v>
+        <v>7085609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,6 +2171,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2319,10 +2309,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168795</v>
+        <v>120168803</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2331,25 +2321,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2359,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498621</v>
+        <v>498551</v>
       </c>
       <c r="R17" t="n">
-        <v>7085423</v>
+        <v>7085554</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,11 +2385,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168804</v>
+        <v>120168802</v>
       </c>
       <c r="B18" t="n">
-        <v>90558</v>
+        <v>57326</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2442,21 +2427,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2466,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498644</v>
+        <v>498710</v>
       </c>
       <c r="R18" t="n">
-        <v>7085616</v>
+        <v>7085620</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,6 +2487,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,10 +2518,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168803</v>
+        <v>120168788</v>
       </c>
       <c r="B19" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2540,25 +2530,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2568,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498551</v>
+        <v>498509</v>
       </c>
       <c r="R19" t="n">
-        <v>7085554</v>
+        <v>7085469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,6 +2594,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2630,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168793</v>
+        <v>120168787</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2646,21 +2641,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2670,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498764</v>
+        <v>498559</v>
       </c>
       <c r="R20" t="n">
-        <v>7085585</v>
+        <v>7085553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,11 +2701,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168809</v>
+        <v>120168797</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2753,21 +2743,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2777,10 +2767,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498628</v>
+        <v>498629</v>
       </c>
       <c r="R21" t="n">
-        <v>7085357</v>
+        <v>7085387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,6 +2803,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,10 +2834,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168808</v>
+        <v>120168804</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,21 +2850,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2879,10 +2874,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498735</v>
+        <v>498644</v>
       </c>
       <c r="R22" t="n">
-        <v>7085566</v>
+        <v>7085616</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2941,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168797</v>
+        <v>120168789</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2981,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498629</v>
+        <v>498570</v>
       </c>
       <c r="R23" t="n">
-        <v>7085387</v>
+        <v>7085548</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120168791</v>
+        <v>120168793</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3088,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498655</v>
+        <v>498764</v>
       </c>
       <c r="R24" t="n">
-        <v>7085609</v>
+        <v>7085585</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3128,7 +3123,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120168807</v>
+        <v>120168800</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3171,21 +3166,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3195,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498649</v>
+        <v>498529</v>
       </c>
       <c r="R25" t="n">
-        <v>7085609</v>
+        <v>7085325</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,6 +3226,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168810</v>
+        <v>120168794</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,37 +1893,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498501</v>
+        <v>498683</v>
       </c>
       <c r="R13" t="n">
-        <v>7085330</v>
+        <v>7085502</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1957,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt i omgivningen</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,7 +1966,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1988,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168794</v>
+        <v>120168810</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2004,34 +2000,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498683</v>
+        <v>498501</v>
       </c>
       <c r="R14" t="n">
-        <v>7085502</v>
+        <v>7085330</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Rikligt i omgivningen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,6 +2076,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168794</v>
+        <v>120168810</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,34 +1893,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498683</v>
+        <v>498501</v>
       </c>
       <c r="R13" t="n">
-        <v>7085502</v>
+        <v>7085330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1960,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Rikligt i omgivningen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,6 +1969,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1984,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168810</v>
+        <v>120168794</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2000,37 +2004,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498501</v>
+        <v>498683</v>
       </c>
       <c r="R14" t="n">
-        <v>7085330</v>
+        <v>7085502</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2068,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt i omgivningen</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,7 +2077,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168807</v>
+        <v>120168806</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498649</v>
+        <v>498639</v>
       </c>
       <c r="R7" t="n">
-        <v>7085609</v>
+        <v>7085616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168809</v>
+        <v>120168807</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498628</v>
+        <v>498649</v>
       </c>
       <c r="R8" t="n">
-        <v>7085357</v>
+        <v>7085609</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168808</v>
+        <v>120168809</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498735</v>
+        <v>498628</v>
       </c>
       <c r="R9" t="n">
-        <v>7085566</v>
+        <v>7085357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168806</v>
+        <v>120168793</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498639</v>
+        <v>498764</v>
       </c>
       <c r="R10" t="n">
-        <v>7085616</v>
+        <v>7085585</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,6 +1637,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1666,7 +1671,7 @@
         <v>120168795</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1773,7 +1778,7 @@
         <v>120168798</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168810</v>
+        <v>120168800</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,37 +1898,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498501</v>
+        <v>498529</v>
       </c>
       <c r="R13" t="n">
-        <v>7085330</v>
+        <v>7085325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1962,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt i omgivningen</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,7 +1971,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1991,7 +1992,7 @@
         <v>120168794</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168791</v>
+        <v>120168792</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2135,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498655</v>
+        <v>498703</v>
       </c>
       <c r="R15" t="n">
-        <v>7085609</v>
+        <v>7085620</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2176,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168792</v>
+        <v>120168808</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2218,21 +2219,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2242,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498703</v>
+        <v>498735</v>
       </c>
       <c r="R16" t="n">
-        <v>7085620</v>
+        <v>7085566</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,11 +2279,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2309,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168803</v>
+        <v>120168797</v>
       </c>
       <c r="B17" t="n">
-        <v>91005</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,25 +2317,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2349,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498551</v>
+        <v>498629</v>
       </c>
       <c r="R17" t="n">
-        <v>7085554</v>
+        <v>7085387</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,6 +2381,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2411,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168802</v>
+        <v>120168788</v>
       </c>
       <c r="B18" t="n">
-        <v>57326</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,16 +2428,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2451,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498710</v>
+        <v>498509</v>
       </c>
       <c r="R18" t="n">
-        <v>7085620</v>
+        <v>7085469</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,7 +2492,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168788</v>
+        <v>120168791</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2558,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498509</v>
+        <v>498655</v>
       </c>
       <c r="R19" t="n">
-        <v>7085469</v>
+        <v>7085609</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168787</v>
+        <v>120168804</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>90576</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,21 +2642,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2665,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498559</v>
+        <v>498644</v>
       </c>
       <c r="R20" t="n">
-        <v>7085553</v>
+        <v>7085616</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168797</v>
+        <v>120168802</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2743,16 +2744,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2767,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498629</v>
+        <v>498710</v>
       </c>
       <c r="R21" t="n">
-        <v>7085387</v>
+        <v>7085620</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2808,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2834,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168804</v>
+        <v>120168789</v>
       </c>
       <c r="B22" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2850,21 +2851,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2874,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498644</v>
+        <v>498570</v>
       </c>
       <c r="R22" t="n">
-        <v>7085616</v>
+        <v>7085548</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,6 +2911,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168789</v>
+        <v>120168803</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>91023</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,25 +2954,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498570</v>
+        <v>498551</v>
       </c>
       <c r="R23" t="n">
-        <v>7085548</v>
+        <v>7085554</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,11 +3018,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120168793</v>
+        <v>120168810</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,34 +3060,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498764</v>
+        <v>498501</v>
       </c>
       <c r="R24" t="n">
-        <v>7085585</v>
+        <v>7085330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,7 +3127,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt i omgivningen</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3132,6 +3136,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3150,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120168800</v>
+        <v>120168787</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,21 +3171,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3190,10 +3195,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498529</v>
+        <v>498559</v>
       </c>
       <c r="R25" t="n">
-        <v>7085325</v>
+        <v>7085553</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,11 +3231,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168807</v>
+        <v>120168808</v>
       </c>
       <c r="B8" t="n">
         <v>90598</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498649</v>
+        <v>498735</v>
       </c>
       <c r="R8" t="n">
-        <v>7085609</v>
+        <v>7085566</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168809</v>
+        <v>120168800</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498628</v>
+        <v>498529</v>
       </c>
       <c r="R9" t="n">
-        <v>7085357</v>
+        <v>7085325</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,6 +1535,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168793</v>
+        <v>120168788</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1601,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498764</v>
+        <v>498509</v>
       </c>
       <c r="R10" t="n">
-        <v>7085585</v>
+        <v>7085469</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1646,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168795</v>
+        <v>120168802</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,16 +1689,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1708,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498621</v>
+        <v>498710</v>
       </c>
       <c r="R11" t="n">
-        <v>7085423</v>
+        <v>7085620</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,7 +1753,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168798</v>
+        <v>120168792</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1815,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498592</v>
+        <v>498703</v>
       </c>
       <c r="R12" t="n">
-        <v>7085385</v>
+        <v>7085620</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1860,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,7 +1887,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168800</v>
+        <v>120168798</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1922,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498529</v>
+        <v>498592</v>
       </c>
       <c r="R13" t="n">
-        <v>7085325</v>
+        <v>7085385</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1967,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168794</v>
+        <v>120168787</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,21 +2010,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2029,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498683</v>
+        <v>498559</v>
       </c>
       <c r="R14" t="n">
-        <v>7085502</v>
+        <v>7085553</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,11 +2070,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168792</v>
+        <v>120168803</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,25 +2108,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498703</v>
+        <v>498551</v>
       </c>
       <c r="R15" t="n">
-        <v>7085620</v>
+        <v>7085554</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,11 +2172,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168808</v>
+        <v>120168791</v>
       </c>
       <c r="B16" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2219,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2243,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498735</v>
+        <v>498655</v>
       </c>
       <c r="R16" t="n">
-        <v>7085566</v>
+        <v>7085609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2279,6 +2274,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168797</v>
+        <v>120168804</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498629</v>
+        <v>498644</v>
       </c>
       <c r="R17" t="n">
-        <v>7085387</v>
+        <v>7085616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,11 +2381,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168788</v>
+        <v>120168807</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2428,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498509</v>
+        <v>498649</v>
       </c>
       <c r="R18" t="n">
-        <v>7085469</v>
+        <v>7085609</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,11 +2483,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168791</v>
+        <v>120168810</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,34 +2525,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498655</v>
+        <v>498501</v>
       </c>
       <c r="R19" t="n">
-        <v>7085609</v>
+        <v>7085330</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,7 +2592,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt i omgivningen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,6 +2601,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2626,10 +2620,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168804</v>
+        <v>120168794</v>
       </c>
       <c r="B20" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2642,21 +2636,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498644</v>
+        <v>498683</v>
       </c>
       <c r="R20" t="n">
-        <v>7085616</v>
+        <v>7085502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,6 +2696,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168802</v>
+        <v>120168793</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,16 +2743,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2768,10 +2767,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498710</v>
+        <v>498764</v>
       </c>
       <c r="R21" t="n">
-        <v>7085620</v>
+        <v>7085585</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,7 +2807,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168803</v>
+        <v>120168809</v>
       </c>
       <c r="B23" t="n">
-        <v>91023</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2954,25 +2953,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2982,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498551</v>
+        <v>498628</v>
       </c>
       <c r="R23" t="n">
-        <v>7085554</v>
+        <v>7085357</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3044,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120168810</v>
+        <v>120168795</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3060,37 +3059,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498501</v>
+        <v>498621</v>
       </c>
       <c r="R24" t="n">
-        <v>7085330</v>
+        <v>7085423</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,7 +3123,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt i omgivningen</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,7 +3132,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3155,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120168787</v>
+        <v>120168797</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3171,21 +3166,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3195,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498559</v>
+        <v>498629</v>
       </c>
       <c r="R25" t="n">
-        <v>7085553</v>
+        <v>7085387</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,6 +3226,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168791</v>
+        <v>120168804</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498655</v>
+        <v>498644</v>
       </c>
       <c r="R16" t="n">
-        <v>7085609</v>
+        <v>7085616</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,11 +2274,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168804</v>
+        <v>120168807</v>
       </c>
       <c r="B17" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498644</v>
+        <v>498649</v>
       </c>
       <c r="R17" t="n">
-        <v>7085616</v>
+        <v>7085609</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168807</v>
+        <v>120168791</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,7 +2442,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498649</v>
+        <v>498655</v>
       </c>
       <c r="R18" t="n">
         <v>7085609</v>
@@ -2483,6 +2478,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1255,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168806</v>
+        <v>120168807</v>
       </c>
       <c r="B7" t="n">
         <v>90598</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498639</v>
+        <v>498649</v>
       </c>
       <c r="R7" t="n">
-        <v>7085616</v>
+        <v>7085609</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168808</v>
+        <v>120168806</v>
       </c>
       <c r="B8" t="n">
         <v>90598</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498735</v>
+        <v>498639</v>
       </c>
       <c r="R8" t="n">
-        <v>7085566</v>
+        <v>7085616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168800</v>
+        <v>120168792</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498529</v>
+        <v>498703</v>
       </c>
       <c r="R9" t="n">
-        <v>7085325</v>
+        <v>7085620</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168788</v>
+        <v>120168803</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498509</v>
+        <v>498551</v>
       </c>
       <c r="R10" t="n">
-        <v>7085469</v>
+        <v>7085554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,11 +1642,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168802</v>
+        <v>120168793</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,16 +1684,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1713,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498710</v>
+        <v>498764</v>
       </c>
       <c r="R11" t="n">
-        <v>7085620</v>
+        <v>7085585</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1748,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168792</v>
+        <v>120168797</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1820,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498703</v>
+        <v>498629</v>
       </c>
       <c r="R12" t="n">
-        <v>7085620</v>
+        <v>7085387</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1855,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,7 +1882,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168798</v>
+        <v>120168794</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1927,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498592</v>
+        <v>498683</v>
       </c>
       <c r="R13" t="n">
-        <v>7085385</v>
+        <v>7085502</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1962,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168787</v>
+        <v>120168809</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,21 +2005,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2034,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498559</v>
+        <v>498628</v>
       </c>
       <c r="R14" t="n">
-        <v>7085553</v>
+        <v>7085357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168803</v>
+        <v>120168795</v>
       </c>
       <c r="B15" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,25 +2103,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2136,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498551</v>
+        <v>498621</v>
       </c>
       <c r="R15" t="n">
-        <v>7085554</v>
+        <v>7085423</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,6 +2167,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168804</v>
+        <v>120168788</v>
       </c>
       <c r="B16" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498644</v>
+        <v>498509</v>
       </c>
       <c r="R16" t="n">
-        <v>7085616</v>
+        <v>7085469</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,6 +2274,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168807</v>
+        <v>120168789</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498649</v>
+        <v>498570</v>
       </c>
       <c r="R17" t="n">
-        <v>7085609</v>
+        <v>7085548</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,6 +2381,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168791</v>
+        <v>120168810</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,34 +2428,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498655</v>
+        <v>498501</v>
       </c>
       <c r="R18" t="n">
-        <v>7085609</v>
+        <v>7085330</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2495,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt i omgivningen</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2491,6 +2504,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2509,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168810</v>
+        <v>120168808</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,37 +2539,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498501</v>
+        <v>498735</v>
       </c>
       <c r="R19" t="n">
-        <v>7085330</v>
+        <v>7085566</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,18 +2601,12 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt i omgivningen</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2620,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168794</v>
+        <v>120168800</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2660,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498683</v>
+        <v>498529</v>
       </c>
       <c r="R20" t="n">
-        <v>7085502</v>
+        <v>7085325</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,7 +2705,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2727,7 +2732,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168793</v>
+        <v>120168791</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2767,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498764</v>
+        <v>498655</v>
       </c>
       <c r="R21" t="n">
-        <v>7085585</v>
+        <v>7085609</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2812,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2834,10 +2839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168789</v>
+        <v>120168787</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2850,21 +2855,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2874,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498570</v>
+        <v>498559</v>
       </c>
       <c r="R22" t="n">
-        <v>7085548</v>
+        <v>7085553</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,11 +2915,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2941,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168809</v>
+        <v>120168798</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,21 +2957,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498628</v>
+        <v>498592</v>
       </c>
       <c r="R23" t="n">
-        <v>7085357</v>
+        <v>7085385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,6 +3017,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,10 +3048,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120168795</v>
+        <v>120168804</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,21 +3064,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3088,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498621</v>
+        <v>498644</v>
       </c>
       <c r="R24" t="n">
-        <v>7085423</v>
+        <v>7085616</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,11 +3124,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120168797</v>
+        <v>120168802</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,16 +3166,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498629</v>
+        <v>498710</v>
       </c>
       <c r="R25" t="n">
-        <v>7085387</v>
+        <v>7085620</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168809</v>
+        <v>120168795</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498628</v>
+        <v>498621</v>
       </c>
       <c r="R14" t="n">
-        <v>7085357</v>
+        <v>7085423</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,6 +2065,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168795</v>
+        <v>120168788</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2131,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498621</v>
+        <v>498509</v>
       </c>
       <c r="R15" t="n">
-        <v>7085423</v>
+        <v>7085469</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,7 +2203,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168788</v>
+        <v>120168789</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2238,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498509</v>
+        <v>498570</v>
       </c>
       <c r="R16" t="n">
-        <v>7085469</v>
+        <v>7085548</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,7 +2283,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168789</v>
+        <v>120168809</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,21 +2326,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498570</v>
+        <v>498628</v>
       </c>
       <c r="R17" t="n">
-        <v>7085548</v>
+        <v>7085357</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,11 +2386,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168806</v>
+        <v>120168810</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1373,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498639</v>
+        <v>498501</v>
       </c>
       <c r="R8" t="n">
-        <v>7085616</v>
+        <v>7085330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,12 +1438,18 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt i omgivningen</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1566,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168803</v>
+        <v>120168794</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,25 +1587,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498551</v>
+        <v>498683</v>
       </c>
       <c r="R10" t="n">
-        <v>7085554</v>
+        <v>7085502</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,6 +1651,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168793</v>
+        <v>120168787</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,21 +1698,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498764</v>
+        <v>498559</v>
       </c>
       <c r="R11" t="n">
-        <v>7085585</v>
+        <v>7085553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,11 +1758,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,7 +1784,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168797</v>
+        <v>120168791</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1815,10 +1824,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498629</v>
+        <v>498655</v>
       </c>
       <c r="R12" t="n">
-        <v>7085387</v>
+        <v>7085609</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1864,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168794</v>
+        <v>120168809</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1898,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1922,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498683</v>
+        <v>498628</v>
       </c>
       <c r="R13" t="n">
-        <v>7085502</v>
+        <v>7085357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,11 +1967,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168795</v>
+        <v>120168804</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,21 +2009,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2029,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498621</v>
+        <v>498644</v>
       </c>
       <c r="R14" t="n">
-        <v>7085423</v>
+        <v>7085616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,11 +2069,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168788</v>
+        <v>120168806</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2136,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498509</v>
+        <v>498639</v>
       </c>
       <c r="R15" t="n">
-        <v>7085469</v>
+        <v>7085616</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,11 +2171,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,7 +2197,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168789</v>
+        <v>120168788</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2243,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498570</v>
+        <v>498509</v>
       </c>
       <c r="R16" t="n">
-        <v>7085548</v>
+        <v>7085469</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,7 +2277,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2304,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168809</v>
+        <v>120168795</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2326,21 +2320,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2350,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498628</v>
+        <v>498621</v>
       </c>
       <c r="R17" t="n">
-        <v>7085357</v>
+        <v>7085423</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,6 +2380,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168810</v>
+        <v>120168797</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2428,37 +2427,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498501</v>
+        <v>498629</v>
       </c>
       <c r="R18" t="n">
-        <v>7085330</v>
+        <v>7085387</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,7 +2491,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt i omgivningen</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,7 +2500,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2523,10 +2518,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168808</v>
+        <v>120168802</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2539,21 +2534,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2563,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498735</v>
+        <v>498710</v>
       </c>
       <c r="R19" t="n">
-        <v>7085566</v>
+        <v>7085620</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,6 +2594,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168800</v>
+        <v>120168798</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498529</v>
+        <v>498592</v>
       </c>
       <c r="R20" t="n">
-        <v>7085325</v>
+        <v>7085385</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,7 +2732,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168791</v>
+        <v>120168789</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498655</v>
+        <v>498570</v>
       </c>
       <c r="R21" t="n">
-        <v>7085609</v>
+        <v>7085548</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168787</v>
+        <v>120168803</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,25 +2851,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498559</v>
+        <v>498551</v>
       </c>
       <c r="R22" t="n">
-        <v>7085553</v>
+        <v>7085554</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168798</v>
+        <v>120168808</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,21 +2957,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498592</v>
+        <v>498735</v>
       </c>
       <c r="R23" t="n">
-        <v>7085385</v>
+        <v>7085566</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,11 +3017,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3048,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120168804</v>
+        <v>120168793</v>
       </c>
       <c r="B24" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3064,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3088,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498644</v>
+        <v>498764</v>
       </c>
       <c r="R24" t="n">
-        <v>7085616</v>
+        <v>7085585</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,6 +3119,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120168802</v>
+        <v>120168800</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,16 +3166,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498710</v>
+        <v>498529</v>
       </c>
       <c r="R25" t="n">
-        <v>7085620</v>
+        <v>7085325</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168807</v>
+        <v>120168787</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498649</v>
+        <v>498559</v>
       </c>
       <c r="R7" t="n">
-        <v>7085609</v>
+        <v>7085553</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168810</v>
+        <v>120168808</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,37 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498501</v>
+        <v>498735</v>
       </c>
       <c r="R8" t="n">
-        <v>7085330</v>
+        <v>7085566</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,18 +1435,12 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt i omgivningen</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1468,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168792</v>
+        <v>120168795</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1508,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498703</v>
+        <v>498621</v>
       </c>
       <c r="R9" t="n">
-        <v>7085620</v>
+        <v>7085423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1539,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168794</v>
+        <v>120168800</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1615,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498683</v>
+        <v>498529</v>
       </c>
       <c r="R10" t="n">
-        <v>7085502</v>
+        <v>7085325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1646,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168787</v>
+        <v>120168798</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1722,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498559</v>
+        <v>498592</v>
       </c>
       <c r="R11" t="n">
-        <v>7085553</v>
+        <v>7085385</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,6 +1749,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168791</v>
+        <v>120168809</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,21 +1796,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1824,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498655</v>
+        <v>498628</v>
       </c>
       <c r="R12" t="n">
-        <v>7085609</v>
+        <v>7085357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,11 +1856,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168809</v>
+        <v>120168797</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,21 +1898,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498628</v>
+        <v>498629</v>
       </c>
       <c r="R13" t="n">
-        <v>7085357</v>
+        <v>7085387</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,6 +1958,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168806</v>
+        <v>120168789</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,21 +2107,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2135,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498639</v>
+        <v>498570</v>
       </c>
       <c r="R15" t="n">
-        <v>7085616</v>
+        <v>7085548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,6 +2167,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168788</v>
+        <v>120168802</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,16 +2214,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2237,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498509</v>
+        <v>498710</v>
       </c>
       <c r="R16" t="n">
-        <v>7085469</v>
+        <v>7085620</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2278,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,7 +2305,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168795</v>
+        <v>120168788</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2344,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498621</v>
+        <v>498509</v>
       </c>
       <c r="R17" t="n">
-        <v>7085423</v>
+        <v>7085469</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,7 +2412,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168797</v>
+        <v>120168794</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2451,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498629</v>
+        <v>498683</v>
       </c>
       <c r="R18" t="n">
-        <v>7085387</v>
+        <v>7085502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,7 +2492,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168802</v>
+        <v>120168793</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,16 +2535,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2558,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498710</v>
+        <v>498764</v>
       </c>
       <c r="R19" t="n">
-        <v>7085620</v>
+        <v>7085585</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,7 +2599,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168798</v>
+        <v>120168803</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,25 +2638,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2665,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498592</v>
+        <v>498551</v>
       </c>
       <c r="R20" t="n">
-        <v>7085385</v>
+        <v>7085554</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,11 +2702,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,7 +2728,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168789</v>
+        <v>120168792</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2772,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498570</v>
+        <v>498703</v>
       </c>
       <c r="R21" t="n">
-        <v>7085548</v>
+        <v>7085620</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2812,7 +2808,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168803</v>
+        <v>120168807</v>
       </c>
       <c r="B22" t="n">
-        <v>91023</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,25 +2847,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2879,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498551</v>
+        <v>498649</v>
       </c>
       <c r="R22" t="n">
-        <v>7085554</v>
+        <v>7085609</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2941,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168808</v>
+        <v>120168791</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2981,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498735</v>
+        <v>498655</v>
       </c>
       <c r="R23" t="n">
-        <v>7085566</v>
+        <v>7085609</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,6 +3013,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120168793</v>
+        <v>120168810</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,34 +3060,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498764</v>
+        <v>498501</v>
       </c>
       <c r="R24" t="n">
-        <v>7085585</v>
+        <v>7085330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,7 +3127,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt i omgivningen</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3132,6 +3136,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3150,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120168800</v>
+        <v>120168806</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,21 +3171,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3190,10 +3195,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498529</v>
+        <v>498639</v>
       </c>
       <c r="R25" t="n">
-        <v>7085325</v>
+        <v>7085616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,11 +3231,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168787</v>
+        <v>120168795</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498559</v>
+        <v>498621</v>
       </c>
       <c r="R7" t="n">
-        <v>7085553</v>
+        <v>7085423</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,6 +1331,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168808</v>
+        <v>120168810</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1378,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498735</v>
+        <v>498501</v>
       </c>
       <c r="R8" t="n">
-        <v>7085566</v>
+        <v>7085330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,12 +1443,18 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt i omgivningen</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1459,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168795</v>
+        <v>120168787</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1489,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498621</v>
+        <v>498559</v>
       </c>
       <c r="R9" t="n">
-        <v>7085423</v>
+        <v>7085553</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,11 +1549,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168800</v>
+        <v>120168804</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498529</v>
+        <v>498644</v>
       </c>
       <c r="R10" t="n">
-        <v>7085325</v>
+        <v>7085616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,11 +1651,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168798</v>
+        <v>120168808</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,21 +1693,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498592</v>
+        <v>498735</v>
       </c>
       <c r="R11" t="n">
-        <v>7085385</v>
+        <v>7085566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,11 +1753,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,7 +1779,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168809</v>
+        <v>120168806</v>
       </c>
       <c r="B12" t="n">
         <v>90598</v>
@@ -1820,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498628</v>
+        <v>498639</v>
       </c>
       <c r="R12" t="n">
-        <v>7085357</v>
+        <v>7085616</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168797</v>
+        <v>120168803</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,25 +1893,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1922,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498629</v>
+        <v>498551</v>
       </c>
       <c r="R13" t="n">
-        <v>7085387</v>
+        <v>7085554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,11 +1957,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168804</v>
+        <v>120168793</v>
       </c>
       <c r="B14" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2029,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498644</v>
+        <v>498764</v>
       </c>
       <c r="R14" t="n">
-        <v>7085616</v>
+        <v>7085585</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,6 +2059,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,7 +2090,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168789</v>
+        <v>120168791</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2131,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498570</v>
+        <v>498655</v>
       </c>
       <c r="R15" t="n">
-        <v>7085548</v>
+        <v>7085609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168802</v>
+        <v>120168809</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2238,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498710</v>
+        <v>498628</v>
       </c>
       <c r="R16" t="n">
-        <v>7085620</v>
+        <v>7085357</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,11 +2273,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,7 +2299,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168788</v>
+        <v>120168798</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2345,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498509</v>
+        <v>498592</v>
       </c>
       <c r="R17" t="n">
-        <v>7085469</v>
+        <v>7085385</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2412,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168794</v>
+        <v>120168802</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2428,16 +2422,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2452,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498683</v>
+        <v>498710</v>
       </c>
       <c r="R18" t="n">
-        <v>7085502</v>
+        <v>7085620</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2486,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,7 +2513,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168793</v>
+        <v>120168794</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2559,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498764</v>
+        <v>498683</v>
       </c>
       <c r="R19" t="n">
-        <v>7085585</v>
+        <v>7085502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,7 +2593,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2626,10 +2620,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168803</v>
+        <v>120168789</v>
       </c>
       <c r="B20" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2638,25 +2632,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498551</v>
+        <v>498570</v>
       </c>
       <c r="R20" t="n">
-        <v>7085554</v>
+        <v>7085548</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,6 +2696,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168792</v>
+        <v>120168807</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,21 +2743,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2768,10 +2767,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498703</v>
+        <v>498649</v>
       </c>
       <c r="R21" t="n">
-        <v>7085620</v>
+        <v>7085609</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,11 +2803,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168807</v>
+        <v>120168797</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,21 +2845,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2875,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498649</v>
+        <v>498629</v>
       </c>
       <c r="R22" t="n">
-        <v>7085609</v>
+        <v>7085387</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,6 +2905,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168791</v>
+        <v>120168792</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2977,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498655</v>
+        <v>498703</v>
       </c>
       <c r="R23" t="n">
-        <v>7085609</v>
+        <v>7085620</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3016,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120168810</v>
+        <v>120168800</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3060,37 +3059,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498501</v>
+        <v>498529</v>
       </c>
       <c r="R24" t="n">
-        <v>7085330</v>
+        <v>7085325</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,7 +3123,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt i omgivningen</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,7 +3132,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3155,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120168806</v>
+        <v>120168788</v>
       </c>
       <c r="B25" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3171,21 +3166,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3195,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498639</v>
+        <v>498509</v>
       </c>
       <c r="R25" t="n">
-        <v>7085616</v>
+        <v>7085469</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,6 +3226,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1255,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168795</v>
+        <v>120168793</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498621</v>
+        <v>498764</v>
       </c>
       <c r="R7" t="n">
-        <v>7085423</v>
+        <v>7085585</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168810</v>
+        <v>120168803</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,41 +1374,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498501</v>
+        <v>498551</v>
       </c>
       <c r="R8" t="n">
-        <v>7085330</v>
+        <v>7085554</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,18 +1440,12 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt i omgivningen</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1473,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168787</v>
+        <v>120168794</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498559</v>
+        <v>498683</v>
       </c>
       <c r="R9" t="n">
-        <v>7085553</v>
+        <v>7085502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,6 +1540,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168804</v>
+        <v>120168809</v>
       </c>
       <c r="B10" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498644</v>
+        <v>498628</v>
       </c>
       <c r="R10" t="n">
-        <v>7085616</v>
+        <v>7085357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168808</v>
+        <v>120168806</v>
       </c>
       <c r="B11" t="n">
         <v>90598</v>
@@ -1717,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498735</v>
+        <v>498639</v>
       </c>
       <c r="R11" t="n">
-        <v>7085566</v>
+        <v>7085616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168806</v>
+        <v>120168792</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,21 +1791,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1819,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498639</v>
+        <v>498703</v>
       </c>
       <c r="R12" t="n">
-        <v>7085616</v>
+        <v>7085620</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,6 +1851,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168803</v>
+        <v>120168787</v>
       </c>
       <c r="B13" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,25 +1894,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1921,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498551</v>
+        <v>498559</v>
       </c>
       <c r="R13" t="n">
-        <v>7085554</v>
+        <v>7085553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +1984,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168793</v>
+        <v>120168798</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2023,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498764</v>
+        <v>498592</v>
       </c>
       <c r="R14" t="n">
-        <v>7085585</v>
+        <v>7085385</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2064,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168809</v>
+        <v>120168802</v>
       </c>
       <c r="B16" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2237,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498628</v>
+        <v>498710</v>
       </c>
       <c r="R16" t="n">
-        <v>7085357</v>
+        <v>7085620</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,6 +2274,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2299,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168798</v>
+        <v>120168808</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2339,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498592</v>
+        <v>498735</v>
       </c>
       <c r="R17" t="n">
-        <v>7085385</v>
+        <v>7085566</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,11 +2381,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168802</v>
+        <v>120168789</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,16 +2423,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2446,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498710</v>
+        <v>498570</v>
       </c>
       <c r="R18" t="n">
-        <v>7085620</v>
+        <v>7085548</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,7 +2487,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,7 +2514,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168794</v>
+        <v>120168797</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2553,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498683</v>
+        <v>498629</v>
       </c>
       <c r="R19" t="n">
-        <v>7085502</v>
+        <v>7085387</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,7 +2594,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2620,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168789</v>
+        <v>120168810</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2636,34 +2637,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mannabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498570</v>
+        <v>498501</v>
       </c>
       <c r="R20" t="n">
-        <v>7085548</v>
+        <v>7085330</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,7 +2704,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Rikligt i omgivningen</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2709,6 +2713,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2727,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168807</v>
+        <v>120168795</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2743,21 +2748,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2767,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498649</v>
+        <v>498621</v>
       </c>
       <c r="R21" t="n">
-        <v>7085609</v>
+        <v>7085423</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,6 +2808,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,10 +2839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168797</v>
+        <v>120168807</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2845,21 +2855,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2869,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498629</v>
+        <v>498649</v>
       </c>
       <c r="R22" t="n">
-        <v>7085387</v>
+        <v>7085609</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,11 +2915,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,7 +2941,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168792</v>
+        <v>120168800</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2976,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498703</v>
+        <v>498529</v>
       </c>
       <c r="R23" t="n">
-        <v>7085620</v>
+        <v>7085325</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,7 +3021,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,7 +3048,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120168800</v>
+        <v>120168788</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3083,10 +3088,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498529</v>
+        <v>498509</v>
       </c>
       <c r="R24" t="n">
-        <v>7085325</v>
+        <v>7085469</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,7 +3128,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120168788</v>
+        <v>120168804</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,21 +3171,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3190,10 +3195,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498509</v>
+        <v>498644</v>
       </c>
       <c r="R25" t="n">
-        <v>7085469</v>
+        <v>7085616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,11 +3231,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 23632-2024 artfynd.xlsx
+++ b/artfynd/A 23632-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168793</v>
+        <v>120168803</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,25 +1267,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498764</v>
+        <v>498551</v>
       </c>
       <c r="R7" t="n">
-        <v>7085585</v>
+        <v>7085554</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,11 +1331,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168803</v>
+        <v>120168793</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498551</v>
+        <v>498764</v>
       </c>
       <c r="R8" t="n">
-        <v>7085554</v>
+        <v>7085585</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,6 +1433,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
